--- a/HI02H04_L02_S01_dist/VO_Manifest.xlsx
+++ b/HI02H04_L02_S01_dist/VO_Manifest.xlsx
@@ -1185,12 +1185,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>vo_celebrate</t>
+          <t>vo_cel_prompt</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>शाबाश! आपने पूरी कहानी ध्यान से पढ़ी और सभी प्रश्नों के उत्तर दे दिए।</t>
+          <t>बहुत बढ़िया, दोस्त! तुमने कमाल कर दिया!</t>
         </is>
       </c>
     </row>

--- a/HI02H04_L02_S01_dist/VO_Manifest.xlsx
+++ b/HI02H04_L02_S01_dist/VO_Manifest.xlsx
@@ -674,7 +674,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>शाबाश! सही जगह।</t>
+          <t>शाबाश! सही जवाब।</t>
         </is>
       </c>
     </row>

--- a/HI02H04_L02_S01_dist/VO_Manifest.xlsx
+++ b/HI02H04_L02_S01_dist/VO_Manifest.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>वह खिलौनों से खेलने लगा।</t>
+          <t>फिर वह खिलौनों से खेलने लगा।</t>
         </is>
       </c>
     </row>

--- a/HI02H04_L02_S01_dist/VO_Manifest.xlsx
+++ b/HI02H04_L02_S01_dist/VO_Manifest.xlsx
@@ -602,7 +602,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>वह थककर सो गया।</t>
+          <t>और वह थककर सो गया।</t>
         </is>
       </c>
     </row>

--- a/HI02H04_L02_S01_dist/VO_Manifest.xlsx
+++ b/HI02H04_L02_S01_dist/VO_Manifest.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>दोपहर का खाना हो चुका था।</t>
+          <t>दोपहर के समय माधव अपनी माँ के साथ खाना खा रहा था।</t>
         </is>
       </c>
     </row>

--- a/HI02H04_L02_S01_dist/VO_Manifest.xlsx
+++ b/HI02H04_L02_S01_dist/VO_Manifest.xlsx
@@ -518,7 +518,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>माधव की माँ उसे सुलाने लगी।</t>
+          <t>खाने के बाद, माधव की माँ उसे सुलाने लगी।</t>
         </is>
       </c>
     </row>

--- a/HI02H04_L02_S01_dist/VO_Manifest.xlsx
+++ b/HI02H04_L02_S01_dist/VO_Manifest.xlsx
@@ -914,7 +914,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>वाह! अब आपकी बारी।</t>
+          <t>अब आपकी बारी!</t>
         </is>
       </c>
     </row>

--- a/HI02H04_L02_S01_dist/VO_Manifest.xlsx
+++ b/HI02H04_L02_S01_dist/VO_Manifest.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>दोपहर के समय माधव अपनी माँ के साथ खाना खा रहा था।</t>
+          <t>माधव अपनी माँ के साथ खाना खा रहा था।</t>
         </is>
       </c>
     </row>
